--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -629,7 +629,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 13:34 UTC</t>
+          <t>Generated: 2026-06-16 13:42 UTC</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::currentUser</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -816,34 +816,34 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>e2e_tests\appium_mobile\test_cases\auth.test.js</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::currentUser</t>
+          <t>firestore://users</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>firestore://users</t>
+          <t>firestore://aptitude_history</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>firestore://aptitude_history</t>
+          <t>firestore://technical_history</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>firestore://technical_history</t>
+          <t>firestore://hr_history</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>firestore://hr_history</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1044,130 +1044,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>All headers present: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security [POST-FIX]</t>
+          <t>All headers present: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security</t>
         </is>
       </c>
       <c r="H3" s="16" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Add the following headers to firebase.json hosting headers config: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>.env.example, .gitignore, automated_test/SECRET_ROTATION_REQUIRED.md</t>
+          <t>automated_test/SECRET_ROTATION_REQUIRED.md</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Created .env.example template; Added to .gitignore: .env, *.env, .env.local, .env.production; Created SECRET_ROTATION_REQUIRED.md with rotation instructions</t>
+          <t>Created SECRET_ROTATION_REQUIRED.md with rotation instructions</t>
         </is>
       </c>
     </row>
@@ -1680,31 +1680,27 @@
           <t>TC-SEC-002</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Yes ✅</t>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>No ❌</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>APPLIED</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>firebase.json</t>
-        </is>
-      </c>
+          <t>Manual Fix Required</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Pending Re-test</t>
+          <t>Pending Manual Review</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Added 7 security header(s): X-Frame-Options, X-Content-Type-Options, X-XSS-Protection, Referrer-Policy, Permissions-Policy, Content-Security-Policy, Strict-Transport-Security</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1923,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.579006+00:00</t>
+          <t>2026-06-16T13:42:57.755292+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1957,7 +1953,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H2" s="15" t="inlineStr">
@@ -1969,7 +1965,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.579640+00:00</t>
+          <t>2026-06-16T13:42:57.755819+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2002,16 +1998,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.629082+00:00</t>
+          <t>2026-06-16T13:42:57.776140+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2041,7 +2037,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H4" s="15" t="inlineStr">
@@ -2053,7 +2049,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.669095+00:00</t>
+          <t>2026-06-16T13:42:57.789037+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2083,7 +2079,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
@@ -2095,7 +2091,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.671843+00:00</t>
+          <t>2026-06-16T13:42:57.789985+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2137,7 +2133,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.672507+00:00</t>
+          <t>2026-06-16T13:42:57.790458+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,18 +64,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00BE4B00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
@@ -88,19 +76,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00276221"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00BE4B00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -116,7 +92,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -140,22 +116,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,36 +186,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -629,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 13:34 UTC</t>
+          <t>Generated: 2026-06-16 14:01 UTC</t>
         </is>
       </c>
     </row>
@@ -677,7 +636,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -687,9 +646,9 @@
           <t>Failed ❌</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -699,9 +658,9 @@
           <t>Critical 🔴</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -711,9 +670,9 @@
           <t>High 🟠</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -735,7 +694,7 @@
           <t>Low 🔵</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -794,350 +753,350 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>firebase-auth::currentUser</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>lib\main.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>firestore://users</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Firestore</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\analytics\analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>firestore://aptitude_history</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Firebase/Firestore</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>lib\screens\analytics\analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>firestore://technical_history</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Firestore</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\analytics\analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>firestore://hr_history</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Firebase/Firestore</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>lib\screens\analytics\analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\analytics\analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>lib\screens\auth\login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\auth\login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::signOut</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>e2e_tests\appium_mobile\test_cases\auth.test.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>lib\screens\auth\login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>firebase-auth::currentUser</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>firebase-auth::createUserWithEmailAndPassword</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>lib\main.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\auth\register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>firestore://users</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>firestore://assignments</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib\screens\campus\add_assignment_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>firestore://aptitude_history</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib\screens\campus\add_class_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>firestore://technical_history</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>firestore://attendance</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>firestore://hr_history</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Auth</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>anonymous / authenticated</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\login_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>firebase-auth::signInWithGoogle</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Auth</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>anonymous / authenticated</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\login_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>firebase-auth::createUserWithEmailAndPassword</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Auth</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>anonymous / authenticated</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
           <t>lib\screens\campus\attendance_screen.dart</t>
@@ -1145,7 +1104,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
@@ -1250,9 +1209,9 @@
           <t>TC-SEC-001</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -1277,17 +1236,17 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>1451 potential secrets found [POST-FIX]</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Move Firebase API keys to environment variables or use flutter_dotenv. Consider Firebase App Check to restrict API key misuse.</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1256,7 @@
           <t>TC-SEC-002</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1324,17 +1283,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>All headers present: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security [POST-FIX]</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
+          <t>All headers present: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Add the following headers to firebase.json hosting headers config: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1344,9 +1303,9 @@
           <t>TC-SEC-003</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1371,17 +1330,17 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>2 file(s) perform Firestore writes without visible auth guard</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Auth guards present on all write operations</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Ensure every Firestore write checks FirebaseAuth.instance.currentUser != null before executing. Also enforce server-side rules in Firestore security rules.</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1350,7 @@
           <t>TC-SEC-004</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1421,7 +1380,7 @@
           <t>Input validation present</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1438,7 +1397,7 @@
           <t>TC-SEC-005</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1468,7 +1427,7 @@
           <t>dart not found in PATH — skipped</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
@@ -1485,9 +1444,9 @@
           <t>TC-SEC-006</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1512,17 +1471,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Security rules file not found: firestore.rules; Security rules file not found: storage.rules</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>Rules appear restrictive</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Replace `allow read, write: if true` with proper auth checks: `allow read, write: if request.auth != null &amp;&amp; request.auth.uid == resource.data.uid`</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1491,7 @@
           <t>TC-SEC-007</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1562,7 +1521,7 @@
           <t>All checked packages are at safe versions</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1648,29 +1607,25 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Yes ✅</t>
+          <t>No ❌</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>.env.example, .gitignore, automated_test/SECRET_ROTATION_REQUIRED.md</t>
-        </is>
-      </c>
+          <t>Manual Fix Required</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr"/>
       <c r="E2" s="6" t="inlineStr"/>
       <c r="F2" s="6" t="inlineStr"/>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Pending Re-test</t>
+          <t>Pending Manual Review</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>Created .env.example template; Added to .gitignore: .env, *.env, .env.local, .env.production; Created SECRET_ROTATION_REQUIRED.md with rotation instructions</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1682,29 +1637,25 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Yes ✅</t>
+          <t>No ❌</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>APPLIED</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>firebase.json</t>
-        </is>
-      </c>
+          <t>Manual Fix Required</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Pending Re-test</t>
+          <t>Pending Manual Review</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Added 7 security header(s): X-Frame-Options, X-Content-Type-Options, X-XSS-Protection, Referrer-Policy, Permissions-Policy, Content-Security-Policy, Strict-Transport-Security</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1665,7 @@
           <t>TC-SEC-003</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1734,7 +1685,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Ensure every Firestore write checks FirebaseAuth.instance.currentUser != null before executing. Also enforce server-side rules in Firestore security rules.</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1695,7 @@
           <t>TC-SEC-004</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1774,7 +1725,7 @@
           <t>TC-SEC-005</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1804,7 +1755,7 @@
           <t>TC-SEC-006</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1824,7 +1775,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Replace `allow read, write: if true` with proper auth checks: `allow read, write: if request.auth != null &amp;&amp; request.auth.uid == resource.data.uid`</t>
+          <t>No action required</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1785,7 @@
           <t>TC-SEC-007</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1927,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.579006+00:00</t>
+          <t>2026-06-16T14:01:59.625358+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1957,19 +1908,19 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.579640+00:00</t>
+          <t>2026-06-16T14:01:59.625995+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -2002,16 +1953,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.629082+00:00</t>
+          <t>2026-06-16T14:01:59.657110+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2041,19 +1992,19 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.669095+00:00</t>
+          <t>2026-06-16T14:01:59.681290+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2083,10 +2034,10 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2095,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.671843+00:00</t>
+          <t>2026-06-16T14:01:59.684289+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2128,16 +2079,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T13:34:57.672507+00:00</t>
+          <t>2026-06-16T14:01:59.684889+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2170,7 +2121,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:13 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:13:52.198647+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:13:52.199022+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:13:52.215894+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:13:52.225596+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:13:52.226498+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:13:52.226972+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:36 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:36:09.199845+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:36:09.200244+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:36:09.216485+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:36:09.225905+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:36:09.226912+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:36:09.227298+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:40 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:40:02.685040+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:40:02.685391+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:40:02.699319+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:40:02.707361+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:40:02.708416+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:40:02.708896+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:43 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:43:10.432590+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:43:10.433005+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:43:10.450181+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:43:10.459873+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:43:10.460917+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:43:10.461384+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:45 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:45:51.829846+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:45:51.830155+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:45:51.847163+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:45:51.855749+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:45:51.856571+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:45:51.856885+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:55 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:55:22.682791+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:55:22.683177+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:55:22.700769+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:55:22.710544+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:55:22.711495+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:55:22.711978+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 14:57 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T14:57:15.814942+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T14:57:15.815313+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T14:57:15.831529+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T14:57:15.841138+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T14:57:15.842156+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T14:57:15.842555+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 15:01 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T15:01:23.629554+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T15:01:23.629984+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T15:01:23.646615+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T15:01:23.656095+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T15:01:23.657146+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T15:01:23.657583+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-16 15:32 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-16T15:32:22.569348+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-16T15:32:22.569775+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-16T15:32:22.586110+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-16T15:32:22.596288+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-16T15:32:22.597374+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-16T15:32:22.597866+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-17 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-17T06:59:41.511191+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-17T06:59:41.511565+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-17T06:59:41.528021+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-17T06:59:41.537691+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-17T06:59:41.538672+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-17T06:59:41.539133+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-18 06:43 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-18T06:43:45.803465+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-18T06:43:45.803817+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-18T06:43:45.820020+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-18T06:43:45.829473+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-18T06:43:45.830527+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-18T06:43:45.830965+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-18 15:06 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-18T15:06:42.362649+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-18T15:06:42.363036+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-18T15:06:42.382100+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-18T15:06:42.393204+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-18T15:06:42.394217+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-18T15:06:42.394708+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-18 15:24 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-18T15:24:03.237995+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-18T15:24:03.238425+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-18T15:24:03.256107+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-18T15:24:03.267234+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-18T15:24:03.268273+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-18T15:24:03.268696+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-18 16:14 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-18T16:14:08.754368+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-18T16:14:08.754759+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-18T16:14:08.773581+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-18T16:14:08.784777+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-18T16:14:08.785822+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-18T16:14:08.786310+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-06-18 16:22 UTC</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>lib\main.dart</t>
+          <t>lib/main.dart</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -883,24 +883,24 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://api.groq.com/openai/v1/chat/completions</t>
+          <t>firestore://assignments</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>External HTTP</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -910,34 +910,34 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\analytics\analytics_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>AUTH</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>FIRESTORE</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithEmailAndPassword</t>
+          <t>firestore://attendance</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Firebase/Auth</t>
+          <t>Firebase/Firestore</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>anonymous / authenticated</t>
+          <t>authenticated</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/home_screen.dart</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>firebase-auth::signInWithGoogle</t>
+          <t>firebase-auth::signOut</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/home/profile_screen.dart</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>firebase-auth::signOut</t>
+          <t>firebase-auth::signInWithEmailAndPassword</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>lib\screens\auth\login_screen.dart</t>
+          <t>lib/screens/auth/login_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1003,130 +1003,130 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>firebase-auth::signInWithGoogle</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Firebase/Auth</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>anonymous / authenticated</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/login_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>firebase-auth::createUserWithEmailAndPassword</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Firebase/Auth</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>anonymous / authenticated</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\auth\register_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/auth/register_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://api.groq.com/openai/v1/chat/completions</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>lib/screens/analytics/analytics_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>https://emkc.org/api/v2/piston/execute</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>External HTTP</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>lib/screens/technical/technical_test_screen.dart</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>firestore://assignments</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>firestore://classes</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Firebase/Firestore</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>authenticated</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_assignment_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>firestore://classes</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\add_class_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>FIRESTORE</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>firestore://attendance</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Firebase/Firestore</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>lib\screens\campus\attendance_screen.dart</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://emkc.org/api/v2/piston/execute</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>External HTTP</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>authenticated</t>
-        </is>
-      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>lib\screens\technical\technical_test_screen.dart</t>
+          <t>lib/screens/campus/add_class_screen.dart</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-06-18T16:22:14.236860+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-06-18T16:22:14.237314+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-06-18T16:22:14.256533+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-06-18T16:22:14.267606+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-06-18T16:22:14.268582+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-06-18T16:22:14.269069+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">

--- a/automated_test/security_test_report.xlsx
+++ b/automated_test/security_test_report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
@@ -71,6 +77,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
       <sz val="10"/>
     </font>
     <font>
@@ -92,7 +104,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +124,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -156,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,24 +203,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -588,7 +611,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-16 14:01 UTC</t>
+          <t>Generated: 2026-07-20 17:32 UTC</t>
         </is>
       </c>
     </row>
@@ -636,7 +659,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -646,9 +669,9 @@
           <t>Failed ❌</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -658,9 +681,9 @@
           <t>Critical 🔴</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -694,7 +717,7 @@
           <t>Low 🔵</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -753,7 +776,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
@@ -780,7 +803,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -807,7 +830,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -834,7 +857,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -861,7 +884,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -888,7 +911,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
@@ -915,7 +938,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
@@ -942,7 +965,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
@@ -969,7 +992,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
@@ -996,7 +1019,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>AUTH</t>
         </is>
@@ -1023,7 +1046,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -1050,7 +1073,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -1077,7 +1100,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>FIRESTORE</t>
         </is>
@@ -1104,7 +1127,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
@@ -1209,9 +1232,9 @@
           <t>TC-SEC-001</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -1236,17 +1259,17 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>21 potential secrets found [POST-FIX]</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>No action required</t>
+          <t>Move Firebase API keys to environment variables or use flutter_dotenv. Consider Firebase App Check to restrict API key misuse.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1279,7 @@
           <t>TC-SEC-002</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1286,7 +1309,7 @@
           <t>All headers present: X-Frame-Options, X-Content-Type-Options, Content-Security-Policy, Referrer-Policy, Permissions-Policy, Strict-Transport-Security</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1303,7 +1326,7 @@
           <t>TC-SEC-003</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1333,7 +1356,7 @@
           <t>Auth guards present on all write operations</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1350,7 +1373,7 @@
           <t>TC-SEC-004</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1380,7 +1403,7 @@
           <t>Input validation present</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1397,7 +1420,7 @@
           <t>TC-SEC-005</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1427,7 +1450,7 @@
           <t>dart not found in PATH — skipped</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
@@ -1444,7 +1467,7 @@
           <t>TC-SEC-006</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1474,7 +1497,7 @@
           <t>Rules appear restrictive</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1491,7 +1514,7 @@
           <t>TC-SEC-007</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1521,7 +1544,7 @@
           <t>All checked packages are at safe versions</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1605,27 +1628,31 @@
           <t>TC-SEC-001</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>No ❌</t>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Yes ✅</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Manual Fix Required</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr"/>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>automated_test/SECRET_ROTATION_REQUIRED.md</t>
+        </is>
+      </c>
       <c r="E2" s="6" t="inlineStr"/>
       <c r="F2" s="6" t="inlineStr"/>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Pending Manual Review</t>
+          <t>Pending Re-test</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>No action required</t>
+          <t>Created SECRET_ROTATION_REQUIRED.md with rotation instructions</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1662,7 @@
           <t>TC-SEC-002</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1665,7 +1692,7 @@
           <t>TC-SEC-003</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1695,7 +1722,7 @@
           <t>TC-SEC-004</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1725,7 +1752,7 @@
           <t>TC-SEC-005</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1755,7 +1782,7 @@
           <t>TC-SEC-006</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1785,7 +1812,7 @@
           <t>TC-SEC-007</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>No ❌</t>
         </is>
@@ -1878,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625358+00:00</t>
+          <t>2026-07-20T17:32:52.440472+00:00</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1908,19 +1935,19 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.625995+00:00</t>
+          <t>2026-07-20T17:32:52.441343+00:00</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1953,7 +1980,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1962,7 +1989,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.657110+00:00</t>
+          <t>2026-07-20T17:32:52.486351+00:00</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1992,10 +2019,10 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2004,7 +2031,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.681290+00:00</t>
+          <t>2026-07-20T17:32:52.520168+00:00</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2034,10 +2061,10 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2046,7 +2073,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684289+00:00</t>
+          <t>2026-07-20T17:32:52.525832+00:00</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -2076,10 +2103,10 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2088,7 +2115,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16T14:01:59.684889+00:00</t>
+          <t>2026-07-20T17:32:52.526504+00:00</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2121,7 +2148,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
